--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdfxswapvaluationtrade/TrdFxSwapValuationTrade001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/trdfxswapvaluationtrade/TrdFxSwapValuationTrade001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>交易编码</t>
     <rPh sb="0" eb="2">
@@ -47,51 +47,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>交割日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>即期汇率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易货币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易货币金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对应货币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对应货币金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>折美元金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易手续费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结算服务费</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他费用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>结算金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资金账户</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -106,23 +62,75 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>期限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>清算模式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>定价日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>远期点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>远期全价</t>
+    <t>期限类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应货币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即期汇率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>近端交割日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>近端掉期点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>近端掉期全价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易货币金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>折美元金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远端交割日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远端掉期点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远端掉期全价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易货币金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应货币金额</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交易手续费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算服务费</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他费用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>资金账户</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -478,20 +486,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="14.33203125" customWidth="1"/>
-    <col min="4" max="6" width="14.33203125" style="2" customWidth="1"/>
-    <col min="7" max="11" width="14.33203125" style="1" customWidth="1"/>
-    <col min="12" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="19" width="13.33203125" customWidth="1"/>
-    <col min="20" max="20" width="13" customWidth="1"/>
-    <col min="21" max="21" width="16.109375" customWidth="1"/>
-    <col min="22" max="24" width="13.77734375" customWidth="1"/>
+    <col min="4" max="9" width="14.33203125" style="2" customWidth="1"/>
+    <col min="10" max="23" width="14.33203125" style="1" customWidth="1"/>
+    <col min="24" max="27" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,64 +509,73 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>16</v>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
